--- a/data/trans_orig/IP2002-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP2002-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10962</t>
+          <t>10996</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>4034</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12656</t>
+          <t>12884</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9129</t>
+          <t>9102</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20417</t>
+          <t>20755</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77252</t>
+          <t>77218</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85039</t>
+          <t>85001</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70036</t>
+          <t>69808</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78827</t>
+          <t>78658</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>150488</t>
+          <t>150150</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>161776</t>
+          <t>161803</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,67%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22171</t>
+          <t>21321</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39873</t>
+          <t>38311</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26269</t>
+          <t>26184</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44050</t>
+          <t>44234</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52223</t>
+          <t>52794</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77467</t>
+          <t>76409</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>354443</t>
+          <t>356005</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>372145</t>
+          <t>372995</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>410718</t>
+          <t>410534</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>428499</t>
+          <t>428584</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>771617</t>
+          <t>772675</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>796861</t>
+          <t>796290</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,78%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>5359</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15481</t>
+          <t>15322</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>4733</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13703</t>
+          <t>14200</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12207</t>
+          <t>11766</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26387</t>
+          <t>26048</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>147030</t>
+          <t>147189</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>156965</t>
+          <t>157152</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>133133</t>
+          <t>132636</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>142492</t>
+          <t>142103</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>282960</t>
+          <t>283299</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>297140</t>
+          <t>297581</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35622</t>
+          <t>36410</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57038</t>
+          <t>58466</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40337</t>
+          <t>39551</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61479</t>
+          <t>62268</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>80265</t>
+          <t>81138</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>110640</t>
+          <t>111421</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>588002</t>
+          <t>586574</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>609418</t>
+          <t>608630</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>622818</t>
+          <t>622029</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>643960</t>
+          <t>644746</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1218697</t>
+          <t>1217916</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1249072</t>
+          <t>1248199</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,9%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5825</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15202</t>
+          <t>15079</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4868</t>
+          <t>4946</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15668</t>
+          <t>15037</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13104</t>
+          <t>12304</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26578</t>
+          <t>25693</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73557</t>
+          <t>73680</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82934</t>
+          <t>82935</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66957</t>
+          <t>67588</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77757</t>
+          <t>77679</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>144806</t>
+          <t>145691</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>158280</t>
+          <t>159080</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,82%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14223</t>
+          <t>14529</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29175</t>
+          <t>30370</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,47 +2694,47 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>7,25%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>32276</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>23532</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>42810</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t>6,96%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>32276</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>24074</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>41863</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42401</t>
+          <t>43092</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66445</t>
+          <t>66414</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>389865</t>
+          <t>388670</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>404817</t>
+          <t>404511</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,47 +2807,47 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>92,75%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,53%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>431134</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>420600</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>439878</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
           <t>93,04%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,61%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>620</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>431134</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>421547</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>439336</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,04%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>816005</t>
+          <t>816036</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>840049</t>
+          <t>839358</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,12%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2746</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10669</t>
+          <t>10677</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4136</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13042</t>
+          <t>13932</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8146</t>
+          <t>8430</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20516</t>
+          <t>21230</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>144424</t>
+          <t>144416</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>152347</t>
+          <t>152361</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>142980</t>
+          <t>142090</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>151886</t>
+          <t>151821</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>290600</t>
+          <t>289886</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>302970</t>
+          <t>302686</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27367</t>
+          <t>28359</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47763</t>
+          <t>47592</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37881</t>
+          <t>38496</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61595</t>
+          <t>61143</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71338</t>
+          <t>70205</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>102056</t>
+          <t>101380</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>615128</t>
+          <t>615299</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>635524</t>
+          <t>634532</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>640463</t>
+          <t>640915</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>664177</t>
+          <t>663562</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1262894</t>
+          <t>1263570</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1293612</t>
+          <t>1294745</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,86%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7207</t>
+          <t>7373</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>547</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5372</t>
+          <t>5614</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2464</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9681</t>
+          <t>10035</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49058</t>
+          <t>48892</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55060</t>
+          <t>55044</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62002</t>
+          <t>61760</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66824</t>
+          <t>66827</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113957</t>
+          <t>113603</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>121603</t>
+          <t>121174</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22473</t>
+          <t>22623</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39906</t>
+          <t>40293</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17300</t>
+          <t>16977</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33729</t>
+          <t>32932</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44115</t>
+          <t>44216</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68407</t>
+          <t>67598</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399957</t>
+          <t>399570</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>417390</t>
+          <t>417240</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>430054</t>
+          <t>430851</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>446483</t>
+          <t>446806</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>835239</t>
+          <t>836048</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>859531</t>
+          <t>859430</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,11%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3765</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12594</t>
+          <t>12855</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>3682</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13432</t>
+          <t>13383</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9141</t>
+          <t>9548</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22367</t>
+          <t>22634</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>150109</t>
+          <t>149848</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>158938</t>
+          <t>159222</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>156306</t>
+          <t>156355</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165697</t>
+          <t>166056</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>310074</t>
+          <t>309807</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>323300</t>
+          <t>322893</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31401</t>
+          <t>31165</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52486</t>
+          <t>52117</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26153</t>
+          <t>25286</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45040</t>
+          <t>44593</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61774</t>
+          <t>61321</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90001</t>
+          <t>89220</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>606345</t>
+          <t>606714</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>627430</t>
+          <t>627666</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>655855</t>
+          <t>656302</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>674742</t>
+          <t>675609</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1269725</t>
+          <t>1270506</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1297952</t>
+          <t>1298405</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4822</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4708</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>722</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6424</t>
+          <t>7269</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48877</t>
+          <t>48983</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55212</t>
+          <t>55095</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>107078</t>
+          <t>106233</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112762</t>
+          <t>112780</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16552</t>
+          <t>16226</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35319</t>
+          <t>35244</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14575</t>
+          <t>14858</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32550</t>
+          <t>32790</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34324</t>
+          <t>34159</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60607</t>
+          <t>58551</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>418098</t>
+          <t>418173</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>436865</t>
+          <t>437191</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>473033</t>
+          <t>472793</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>491008</t>
+          <t>490725</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>898394</t>
+          <t>900450</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>924677</t>
+          <t>924842</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,44%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8009</t>
+          <t>8025</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19600</t>
+          <t>20063</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>8861</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23137</t>
+          <t>24939</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20014</t>
+          <t>20252</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38338</t>
+          <t>38210</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>127938</t>
+          <t>127475</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>139529</t>
+          <t>139513</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158942</t>
+          <t>157140</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>173555</t>
+          <t>173218</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>291279</t>
+          <t>291407</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>309603</t>
+          <t>309365</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,86%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29415</t>
+          <t>29073</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50901</t>
+          <t>51263</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27882</t>
+          <t>27386</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50173</t>
+          <t>49894</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61650</t>
+          <t>61889</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>92894</t>
+          <t>91451</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>603753</t>
+          <t>603391</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>625239</t>
+          <t>625581</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>697292</t>
+          <t>697571</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>719583</t>
+          <t>720079</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1309225</t>
+          <t>1310668</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1340469</t>
+          <t>1340230</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,59%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2002-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP2002-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7503</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3927</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12780</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>9,07%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,75%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>15,45%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>6393</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3213</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10996</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3184</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11193</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>7,25%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,46%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>7503</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4034</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>12884</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>9,07%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9102</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20755</t>
+          <t>20799</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>75189</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>69912</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>78765</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>90,93%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>84,55%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,25%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>81821</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>77218</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>85001</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>77021</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>85030</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>92,75%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>87,54%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,36%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>75189</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>69808</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>78658</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>90,93%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>150150</t>
+          <t>150106</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>161803</t>
+          <t>161719</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>82692</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>82692</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>82692</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>88214</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>88214</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>88214</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>82692</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>82692</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>82692</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>33934</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>25599</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>43850</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,46%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,63%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,64%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>29685</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>21321</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>38311</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>22386</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>39038</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>7,53%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,41%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,72%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>33934</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>26184</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>44234</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>7,46%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52794</t>
+          <t>52770</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76409</t>
+          <t>76855</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>420834</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>410918</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>429169</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,54%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,36%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,37%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>550</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>364631</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>356005</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>372995</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>355278</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>371930</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>92,47%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,28%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,59%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>635</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>420834</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>410534</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>428584</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>92,54%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>772675</t>
+          <t>772229</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>796290</t>
+          <t>796314</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,79%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>454768</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>454768</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>454768</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>594</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>394316</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>394316</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>394316</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>686</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>454768</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>454768</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>454768</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8442</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4490</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13982</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,75%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,06%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,52%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>9743</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5359</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>15322</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5675</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>15729</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,43%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>8442</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4733</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>14200</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,75%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11766</t>
+          <t>12170</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26048</t>
+          <t>26140</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>138394</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>132854</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>142346</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,25%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>90,48%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,94%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>152768</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>147189</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>157152</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>146782</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>156836</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>94,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>90,57%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,7%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>138394</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>132636</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>142103</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,25%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>283299</t>
+          <t>283207</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>297581</t>
+          <t>297177</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>146836</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>146836</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>146836</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>162511</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>162511</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>162511</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>146836</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>146836</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>146836</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>49879</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>39689</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>61267</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,29%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,8%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,95%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>45821</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>36410</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>58466</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>35874</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>57442</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>7,1%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5,64%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,06%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>49879</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>39551</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>62268</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>7,29%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>81138</t>
+          <t>81872</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>111421</t>
+          <t>111457</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>955</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>634418</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>623030</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>644608</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>92,71%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,05%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,2%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>895</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>599219</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>586574</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>608630</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>587598</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>609166</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>92,9%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>90,94%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>94,36%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>955</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>634418</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>622029</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>644746</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>92,71%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1217916</t>
+          <t>1217880</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1248199</t>
+          <t>1247465</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,84%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1029</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>684297</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>684297</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>684297</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>963</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>645040</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>645040</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>645040</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1029</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>684297</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>684297</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>684297</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8639</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4457</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>15050</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>10,46%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5,39%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>18,21%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>9770</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5824</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15079</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5841</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>15119</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>11,01%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,56%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16,99%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>8639</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4946</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>15037</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>10,46%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12304</t>
+          <t>12232</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25693</t>
+          <t>26240</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,31%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>73986</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>67575</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>78168</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>89,54%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>81,79%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>94,61%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>78989</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>73680</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>82935</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>73640</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>82918</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>88,99%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>83,01%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>93,44%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>73986</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>67588</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>77679</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>89,54%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>145691</t>
+          <t>145144</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>159080</t>
+          <t>159152</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,86%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>82625</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>82625</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>82625</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>88759</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>88759</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>88759</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>82625</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>82625</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>82625</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>32276</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>23426</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>42226</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,96%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,06%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,11%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>21174</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>14529</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>30370</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>14835</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>29323</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>5,05%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,25%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>32276</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>23532</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>42810</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43092</t>
+          <t>41950</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66414</t>
+          <t>64843</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>431134</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>421184</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>439984</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,04%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,89%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,94%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>576</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>397866</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>388670</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>404511</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>389717</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>404205</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>94,95%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,75%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,53%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>620</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>431134</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>420600</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>439878</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,04%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>816036</t>
+          <t>817607</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>839358</t>
+          <t>840500</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,25%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>463410</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>463410</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>463410</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>606</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>419040</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>419040</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>419040</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>463410</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>463410</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>463410</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7768</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4223</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13950</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,94%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>5728</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2732</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10677</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2695</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>11137</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,69%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,88%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7768</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4201</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>13932</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8430</t>
+          <t>8083</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21230</t>
+          <t>20081</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>148254</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>142072</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>151799</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>95,02%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,06%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,29%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>149365</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>144416</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>152361</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>143956</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>152398</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,31%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93,12%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,24%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>148254</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>142090</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>151821</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>95,02%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>289886</t>
+          <t>291035</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>302686</t>
+          <t>303033</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>156022</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>156022</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>156022</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155093</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155093</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155093</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>156022</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>156022</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>156022</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>48684</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>38427</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>61050</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,93%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,47%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>36672</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>28359</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>47592</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>27318</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>46356</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,53%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,18%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>48684</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>38496</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>61143</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,93%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70205</t>
+          <t>71185</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>101380</t>
+          <t>100463</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>935</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>653374</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>641008</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>663631</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,07%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,3%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,53%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>901</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>626219</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>615299</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>634532</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>616535</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>635573</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,47%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,82%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,72%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>935</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>653374</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>640915</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>663562</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>93,07%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1263570</t>
+          <t>1264487</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1294745</t>
+          <t>1293765</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,78%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>702058</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>702058</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>702058</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>954</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>662891</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>662891</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>662891</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1002</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>702058</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>702058</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>702058</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1975</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5240</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,78%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3393</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1221</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7373</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1264</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7746</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>6,03%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,1%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1975</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5614</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2464</t>
+          <t>2545</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10035</t>
+          <t>10264</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>65399</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>62134</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>66817</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,07%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>92,22%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,17%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>52872</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>48892</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>55044</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>48519</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>55001</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>93,97%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>86,9%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,83%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>65399</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>61760</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>66827</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,07%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113603</t>
+          <t>113374</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>121174</t>
+          <t>121093</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>67374</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>67374</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>67374</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>56265</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>56265</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>56265</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>67374</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>67374</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>67374</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>23933</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>16515</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>33278</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,16%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,18%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>30575</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>22623</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>40293</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>21824</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>40201</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>6,95%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,14%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,16%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>23933</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>16977</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>32932</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,16%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44216</t>
+          <t>43633</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67598</t>
+          <t>67179</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>439850</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>430505</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>447268</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,84%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,82%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,44%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>617</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>409288</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>399570</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>417240</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>399662</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>418039</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>93,05%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,84%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,86%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>439850</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>430851</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>446806</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>94,84%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>836048</t>
+          <t>836467</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>859430</t>
+          <t>860013</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>463783</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>463783</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>463783</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>661</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>439863</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>439863</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>439863</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>659</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>463783</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>463783</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>463783</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4620,67 +4620,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>7809</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3935</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13985</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,24%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>6965</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3481</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12855</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3459</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>12375</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,28%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,9%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7809</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3682</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>13383</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,6%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9548</t>
+          <t>9579</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22634</t>
+          <t>22874</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>161929</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>155753</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>165803</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>95,4%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,76%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,68%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>155738</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>149848</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>159222</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>150328</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>159244</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>95,72%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>92,1%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,86%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>161929</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>156355</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>166056</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>95,4%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>309807</t>
+          <t>309567</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>322893</t>
+          <t>322862</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>169738</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>169738</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>169738</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>162703</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>162703</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>162703</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>169738</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>169738</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>169738</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>33716</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>25408</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>43923</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,63%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,27%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>40933</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>31165</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>52117</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>31333</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>51664</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>6,21%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,73%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,91%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>33716</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>25286</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>44593</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,81%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61321</t>
+          <t>61818</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>89220</t>
+          <t>89187</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>954</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>667179</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>656972</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>675487</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,19%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>93,73%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,37%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>929</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>617898</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>606714</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>627666</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>607167</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>627498</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>93,79%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,09%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,27%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>954</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>667179</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>656302</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>675609</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,19%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1270506</t>
+          <t>1270539</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1298405</t>
+          <t>1297908</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,45%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>700895</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>700895</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>700895</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>988</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>658831</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>658831</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>658831</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>700895</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>700895</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>700895</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4716</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -5582,12 +5582,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4708</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2437</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>686</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7269</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -5645,74 +5645,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>53788</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>49260</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>54933</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,92%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>89,67%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>52363</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>48983</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>97,51%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>91,22%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>44614</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>41425</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>45905</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>97,19%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>90,24%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>58583</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>55095</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>59803</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,96%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>92,13%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>143</t>
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>110946</t>
+          <t>98401</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>106233</t>
+          <t>94665</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112780</t>
+          <t>100152</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>54933</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>54933</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>54933</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>59803</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>59803</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59803</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>113502</t>
+          <t>100838</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>113502</t>
+          <t>100838</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>113502</t>
+          <t>100838</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,107 +5875,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>19884</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12965</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>29158</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,26%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,25%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>24195</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>16226</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>35244</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5,34%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>23350</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>16427</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>32460</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>5,48%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>3,86%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>7,62%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>43234</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>32007</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>55723</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>4,84%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>3,58%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,77%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>21425</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>14858</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>32790</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,24%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>2,94%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>6,49%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>45620</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>34159</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>58551</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>4,76%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -5988,107 +5988,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>446976</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>437702</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>453895</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,74%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,75%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,22%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>595</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>429222</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>418173</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>437191</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>94,66%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,23%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>402763</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>393653</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>409686</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>94,52%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>92,38%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>96,14%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1198</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>849739</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>837250</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>860966</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>95,16%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>93,76%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
         <is>
           <t>96,42%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>484158</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>472793</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>490725</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,76%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>93,51%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>97,06%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1198</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>913381</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>900450</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>924842</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>95,24%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>93,89%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>96,44%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>466860</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>466860</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>466860</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>453417</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>453417</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>453417</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>631</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>505583</t>
+          <t>426113</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>505583</t>
+          <t>426113</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>505583</t>
+          <t>426113</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>959001</t>
+          <t>892973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>959001</t>
+          <t>892973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>959001</t>
+          <t>892973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13265</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8045</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>20918</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,92%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>13319</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8025</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>20063</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,03%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,44%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,6%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14872</t>
+          <t>13639</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8861</t>
+          <t>8890</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24939</t>
+          <t>20537</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>28191</t>
+          <t>26904</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20252</t>
+          <t>19400</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38210</t>
+          <t>37557</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>154131</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>146478</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>159351</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>92,08%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>87,5%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,19%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>134219</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>127475</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>139513</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>90,97%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>86,4%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>94,56%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>167207</t>
+          <t>134661</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>157140</t>
+          <t>127763</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>173218</t>
+          <t>139410</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>301426</t>
+          <t>288792</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>291407</t>
+          <t>278139</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>309365</t>
+          <t>296296</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,85%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>167396</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167396</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167396</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>147538</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>147538</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>147538</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>182079</t>
+          <t>148300</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>182079</t>
+          <t>148300</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182079</t>
+          <t>148300</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>329617</t>
+          <t>315696</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>329617</t>
+          <t>315696</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>329617</t>
+          <t>315696</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>34294</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>24835</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>46040</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,68%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>38849</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>29073</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>51263</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>5,93%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,83%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>37518</t>
+          <t>38281</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27386</t>
+          <t>29150</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49894</t>
+          <t>48865</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>76367</t>
+          <t>72575</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61889</t>
+          <t>59116</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91451</t>
+          <t>87880</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>654896</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>643150</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>664355</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,02%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>93,32%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,4%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>866</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>615805</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>603391</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>625581</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>94,07%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,17%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,56%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>899</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>709947</t>
+          <t>582036</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>697571</t>
+          <t>571452</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>720079</t>
+          <t>591167</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1325752</t>
+          <t>1236932</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1310668</t>
+          <t>1221627</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1340230</t>
+          <t>1250391</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>689190</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>689190</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>689190</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>920</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>654654</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>654654</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>654654</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>946</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>747465</t>
+          <t>620317</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>747465</t>
+          <t>620317</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>747465</t>
+          <t>620317</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1402119</t>
+          <t>1309507</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1402119</t>
+          <t>1309507</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1402119</t>
+          <t>1309507</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
